--- a/myapp/cert_templates/Agreement_Certificate.xlsx
+++ b/myapp/cert_templates/Agreement_Certificate.xlsx
@@ -1,24 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myapp\cert_templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D885FDA-09C0-422B-993F-F3D7EFB3A503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="2865" yWindow="3480" windowWidth="11820" windowHeight="11295" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="inputs" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Agreement Certificate" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="inputs" sheetId="1" r:id="rId1"/>
+    <sheet name="Agreement Certificate" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Agreement Certificate'!$1:$21</definedName>
-    <definedName function="false" hidden="false" name="osa_head" vbProcedure="false">inputs!$B$4</definedName>
-    <definedName function="false" hidden="false" name="program" vbProcedure="false">inputs!$B$3</definedName>
-    <definedName function="false" hidden="false" name="student_name" vbProcedure="false">inputs!$B$2</definedName>
+    <definedName name="osa_head">inputs!$B$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Agreement Certificate'!$1:$21</definedName>
+    <definedName name="program">inputs!$B$3</definedName>
+    <definedName name="student_name">inputs!$B$2</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -29,31 +45,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">student_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lord Jaisson Riberal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BET-COET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">osa_head</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverly M. de Vega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECHNOLOGICAL UNIVERSITY OF THE PHILIPPINES</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>values</t>
+  </si>
+  <si>
+    <t>student_name</t>
+  </si>
+  <si>
+    <t>Lord Jaisson Riberal</t>
+  </si>
+  <si>
+    <t>program</t>
+  </si>
+  <si>
+    <t>BET-COET</t>
+  </si>
+  <si>
+    <t>osa_head</t>
+  </si>
+  <si>
+    <t>Beverly M. de Vega</t>
+  </si>
+  <si>
+    <t>TECHNOLOGICAL UNIVERSITY OF THE PHILIPPINES</t>
   </si>
   <si>
     <t xml:space="preserve">                   CAVITE CAMPUS</t>
@@ -62,50 +78,31 @@
     <t xml:space="preserve">      CQT. Ave., Salawag City of Dasmariñas City, Cavite</t>
   </si>
   <si>
-    <t xml:space="preserve">COMMUNITY SERVICE COMPLETION AGREEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">________________________</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student's Signature over Printed Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head, Office of Student Affairs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date Signed:</t>
+    <t>COMMUNITY SERVICE COMPLETION AGREEMENT</t>
+  </si>
+  <si>
+    <t>________________________</t>
+  </si>
+  <si>
+    <t>Student's Signature over Printed Name</t>
+  </si>
+  <si>
+    <t>Head, Office of Student Affairs</t>
+  </si>
+  <si>
+    <t>Date Signed:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -129,7 +126,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -137,7 +134,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -145,7 +142,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -162,7 +159,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -170,128 +167,97 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>106920</xdr:colOff>
+      <xdr:colOff>71201</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>8280</xdr:rowOff>
+      <xdr:rowOff>32093</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>542520</xdr:colOff>
+      <xdr:colOff>446484</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>118800</xdr:rowOff>
+      <xdr:rowOff>89298</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture 2" descr=""/>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="187560" y="74880"/>
-          <a:ext cx="435600" cy="434520"/>
+          <a:off x="148592" y="97577"/>
+          <a:ext cx="375283" cy="378674"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -308,56 +274,56 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -387,7 +353,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -411,7 +377,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -471,182 +437,190 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="29.14"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="12.75" customHeight="true" zeroHeight="true" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="1.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="27.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="3.15"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="16384" min="6" style="0" width="9.14"/>
+    <col min="1" max="1" width="1.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="1.5703125" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="5.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="2:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" spans="2:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="5" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="str">
-        <f aca="false">"I " &amp; student_name &amp; " from the " &amp; program &amp; " program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance."</f>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="2:4" s="11" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="3" t="str">
+        <f>"I " &amp; student_name &amp; " from the " &amp; program &amp; " program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance."</f>
         <v>I Lord Jaisson Riberal from the BET-COET program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance.</v>
       </c>
-    </row>
-    <row r="9" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="10" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" s="7" customFormat="true" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="2:4" s="11" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10" t="str">
-        <f aca="false">osa_head</f>
+      <c r="C16" s="2"/>
+      <c r="D16" s="12" t="str">
+        <f>osa_head</f>
         <v>Beverly M. de Vega</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
+    <row r="17" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="1"/>
+      <c r="D17" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B19" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:D14"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="8:13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
-  <pageMargins left="0.984027777777778" right="0.984027777777778" top="0.315277777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.98402777777777795" right="0.98402777777777795" top="0.31527777777777799" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/myapp/cert_templates/Agreement_Certificate.xlsx
+++ b/myapp/cert_templates/Agreement_Certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myapp\cert_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D885FDA-09C0-422B-993F-F3D7EFB3A503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31EC362-A30E-4030-B639-F4333C155313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2865" yWindow="3480" windowWidth="11820" windowHeight="11295" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,12 +72,6 @@
     <t>TECHNOLOGICAL UNIVERSITY OF THE PHILIPPINES</t>
   </si>
   <si>
-    <t xml:space="preserve">                   CAVITE CAMPUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      CQT. Ave., Salawag City of Dasmariñas City, Cavite</t>
-  </si>
-  <si>
     <t>COMMUNITY SERVICE COMPLETION AGREEMENT</t>
   </si>
   <si>
@@ -91,6 +85,12 @@
   </si>
   <si>
     <t>Date Signed:</t>
+  </si>
+  <si>
+    <t>CAVITE CAMPUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CQT. Ave., Salawag City of Dasmariñas City, Cavite</t>
   </si>
 </sst>
 </file>
@@ -172,41 +172,41 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -228,16 +228,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>71201</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>164422</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>32093</xdr:rowOff>
+      <xdr:rowOff>30720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>446484</xdr:colOff>
+      <xdr:colOff>324921</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>89298</xdr:rowOff>
+      <xdr:rowOff>87925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -256,8 +256,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="148592" y="97577"/>
-          <a:ext cx="375283" cy="378674"/>
+          <a:off x="164422" y="96662"/>
+          <a:ext cx="380307" cy="379590"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -457,34 +457,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -499,7 +499,7 @@
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.140625" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
@@ -509,101 +509,101 @@
   <sheetData>
     <row r="1" spans="2:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
     </row>
     <row r="3" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="B3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="2:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="5" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
+      <c r="B6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
     </row>
     <row r="7" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="2:4" s="11" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="3" t="str">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="2:4" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="9" t="str">
         <f>"I " &amp; student_name &amp; " from the " &amp; program &amp; " program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance."</f>
         <v>I Lord Jaisson Riberal from the BET-COET program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance.</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="2:4" s="11" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="2:4" s="11" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="2:4" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="12" t="str">
+      <c r="B16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="5" t="str">
         <f>osa_head</f>
         <v>Beverly M. de Vega</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="9" t="s">
-        <v>14</v>
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="19" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="13" t="s">
-        <v>15</v>
+      <c r="B19" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/myapp/cert_templates/Agreement_Certificate.xlsx
+++ b/myapp/cert_templates/Agreement_Certificate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myapp\cert_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31EC362-A30E-4030-B639-F4333C155313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A0DF3E-FCC5-4609-840D-35B0F556ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2865" yWindow="3480" windowWidth="11820" windowHeight="11295" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inputs" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Agreement Certificate'!$1:$21</definedName>
     <definedName name="program">inputs!$B$3</definedName>
     <definedName name="student_name">inputs!$B$2</definedName>
+    <definedName name="title">inputs!$B$5</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>name</t>
   </si>
@@ -91,6 +92,9 @@
   </si>
   <si>
     <t xml:space="preserve"> CQT. Ave., Salawag City of Dasmariñas City, Cavite</t>
+  </si>
+  <si>
+    <t>title</t>
   </si>
 </sst>
 </file>
@@ -196,6 +200,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -203,9 +210,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.28515625" customWidth="1"/>
@@ -486,6 +490,14 @@
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -509,33 +521,33 @@
   <sheetData>
     <row r="1" spans="2:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
     </row>
     <row r="3" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
     </row>
     <row r="5" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
     </row>
     <row r="7" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
@@ -596,8 +608,9 @@
         <v>11</v>
       </c>
       <c r="C17" s="8"/>
-      <c r="D17" s="3" t="s">
-        <v>12</v>
+      <c r="D17" s="3" t="str">
+        <f>title</f>
+        <v>Head, Office of Student Affairs</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/myapp/cert_templates/Agreement_Certificate.xlsx
+++ b/myapp/cert_templates/Agreement_Certificate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\thesis_osa\myapp\cert_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A0DF3E-FCC5-4609-840D-35B0F556ACBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C5FD25-294E-4913-ACBE-AED0E5AA5471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="osa_head">inputs!$B$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Agreement Certificate'!$1:$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Agreement Certificate'!$1:$23</definedName>
     <definedName name="program">inputs!$B$3</definedName>
     <definedName name="student_name">inputs!$B$2</definedName>
     <definedName name="title">inputs!$B$5</definedName>
@@ -76,15 +76,9 @@
     <t>COMMUNITY SERVICE COMPLETION AGREEMENT</t>
   </si>
   <si>
-    <t>________________________</t>
-  </si>
-  <si>
     <t>Student's Signature over Printed Name</t>
   </si>
   <si>
-    <t>Head, Office of Student Affairs</t>
-  </si>
-  <si>
     <t>Date Signed:</t>
   </si>
   <si>
@@ -95,13 +89,19 @@
   </si>
   <si>
     <t>title</t>
+  </si>
+  <si>
+    <t>Officer-In-Charge, Head, Office of Student Affairs</t>
+  </si>
+  <si>
+    <t>_______________________________</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -139,14 +139,6 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -174,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -186,13 +178,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -209,6 +195,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -494,10 +483,10 @@
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -508,7 +497,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.28515625" customWidth="1"/>
@@ -521,33 +510,33 @@
   <sheetData>
     <row r="1" spans="2:4" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="B3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="2:4" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="B4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
     </row>
     <row r="5" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="6" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
@@ -555,81 +544,96 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="2:4" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="9" t="str">
+      <c r="B8" s="7" t="str">
         <f>"I " &amp; student_name &amp; " from the " &amp; program &amp; " program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance."</f>
         <v>I Lord Jaisson Riberal from the BET-COET program, understand that I must complete all pending community service hours before the end of the current semester or before applying for clearance for any academic credential. Failure to comply may result in delayed or denied clearance.</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
     </row>
     <row r="9" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
     </row>
     <row r="11" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
     </row>
     <row r="12" spans="2:4" s="1" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="2:4" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
     </row>
     <row r="15" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="5" t="str">
+      <c r="B16" s="12" t="str">
         <f>osa_head</f>
         <v>Beverly M. de Vega</v>
       </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
     </row>
     <row r="17" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="10" t="str">
+        <f>title</f>
+        <v>Officer-In-Charge, Head, Office of Student Affairs</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="8"/>
-      <c r="D17" s="3" t="str">
-        <f>title</f>
-        <v>Head, Office of Student Affairs</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="2:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="23" spans="2:4" ht="12.75" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:D14"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.98402777777777795" right="0.98402777777777795" top="0.31527777777777799" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
